--- a/Sajjad data/by_country_and_state/Canada/BC.xlsx
+++ b/Sajjad data/by_country_and_state/Canada/BC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="587">
   <si>
     <t>Business Name</t>
   </si>
@@ -464,6 +464,1314 @@
   </si>
   <si>
     <t>2026-10-25T19:35:43.148Z</t>
+  </si>
+  <si>
+    <t>Richmond Public Market Dental</t>
+  </si>
+  <si>
+    <t>+1 604-821-9888</t>
+  </si>
+  <si>
+    <t>8260 Westminster Hwy #2200, Richmond, BC V6X 3Y2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Richmond+Public+Market+Dental/data=!4m7!3m6!1s0x548675cc0abbd653:0x51c2145637367980!8m2!3d49.1698241!4d-123.1332344!16s%2Fg%2F11z3k8cv5b!19sChIJU9a7Csx1hlQRgHk2N1YUwlE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:20:41.596Z</t>
+  </si>
+  <si>
+    <t>Gental Dental</t>
+  </si>
+  <si>
+    <t>+1 604-821-0909</t>
+  </si>
+  <si>
+    <t>6628 River Rd #140, Richmond, BC V7C 0E2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gental+Dental/data=!4m7!3m6!1s0x54860bea5c6a052b:0x9fecac88ad801726!8m2!3d49.1747785!4d-123.1478891!16s%2Fg%2F11z9dsn9h8!19sChIJKwVqXOoLhlQRJheArYis7J8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:20:44.486Z</t>
+  </si>
+  <si>
+    <t>Panda Dental</t>
+  </si>
+  <si>
+    <t>+1 604-278-8769</t>
+  </si>
+  <si>
+    <t>6200 River Rd, Richmond, BC V7C 0B1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Panda+Dental/data=!4m7!3m6!1s0x54860ad254f2a613:0x7e30b69cf2116e8a!8m2!3d49.1741132!4d-123.1495074!16s%2Fg%2F11b7_0ptn0!19sChIJE6byVNIKhlQRim4R8py2MH4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:20:47.410Z</t>
+  </si>
+  <si>
+    <t>Three West Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 604-278-8816</t>
+  </si>
+  <si>
+    <t>6061 Number 3 Rd #110, Richmond, BC V6Y 2B2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Three+West+Dental+Centre/data=!4m7!3m6!1s0x548675335539d29d:0xadf266cb7584af2b!8m2!3d49.1694166!4d-123.1368367!16s%2Fg%2F1txfnvgj!19sChIJndI5VTN1hlQRK6-Edctm8q0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:21:02.059Z</t>
+  </si>
+  <si>
+    <t>Dental clinic, Dr. Chan Jimmy</t>
+  </si>
+  <si>
+    <t>+1 604-231-9684</t>
+  </si>
+  <si>
+    <t>8171 Ackroyd Rd #5055, Richmond, BC V6X 3J9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+clinic,+Dr.+Chan+Jimmy/data=!4m7!3m6!1s0x548675338e2781f3:0x5c706b4b1c4a633c!8m2!3d49.1727456!4d-123.1347955!16s%2Fg%2F1td32r71!19sChIJ84EnjjN1hlQRPGNKHEtrcFw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:21:04.610Z</t>
+  </si>
+  <si>
+    <t>Park Road Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 604-285-0968</t>
+  </si>
+  <si>
+    <t>5951 Minoru Blvd Unit 151, Richmond, BC V6X 4B1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Park+Road+Dental+Centre/data=!4m7!3m6!1s0x54860ab580bf1427:0x9bf3a916152fc07c!8m2!3d49.171145!4d-123.140646!16s%2Fg%2F11cn8s97kk!19sChIJJxS_gLUKhlQRfMAvFRap85s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:21:06.819Z</t>
+  </si>
+  <si>
+    <t>Yaohan Centre Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 604-231-9888</t>
+  </si>
+  <si>
+    <t>3700 Number 3 Rd #2265, Richmond, BC V6X 3X2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yaohan+Centre+Dental+Clinic/data=!4m7!3m6!1s0x5486752798a92635:0x7353f6cab7a754!8m2!3d49.1865584!4d-123.1330368!16s%2Fg%2F1txc6qw7!19sChIJNSapmCd1hlQRVKe3yvZTcwA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:21:09.477Z</t>
+  </si>
+  <si>
+    <t>Lee James K K Dr</t>
+  </si>
+  <si>
+    <t>+1 604-244-3933</t>
+  </si>
+  <si>
+    <t>4400 Hazelbridge Wy, Richmond, BC V6X 3R8, Canada</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lee+James+K+K+Dr/data=!4m7!3m6!1s0x5486752f5b08eac1:0x15ef027fab40e71f!8m2!3d49.1816978!4d-123.1324325!16s%2Fg%2F1vgw89yz!19sChIJweoIWy91hlQRH-dAq38C7xU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:21:11.864Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael Yang Orthodontist</t>
+  </si>
+  <si>
+    <t>+1 604-270-7828</t>
+  </si>
+  <si>
+    <t>6091 Gilbert Rd. #360, Richmond, BC V7C 5L9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+Yang+Orthodontist/data=!4m7!3m6!1s0x54860ba855089d97:0xfbf748b2b7db666d!8m2!3d49.1693047!4d-123.1482128!16s%2Fg%2F11z10m6zgw!19sChIJl50IVagLhlQRbWbbt7JI9_s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:00.508Z</t>
+  </si>
+  <si>
+    <t>Lee Cecilia Dr</t>
+  </si>
+  <si>
+    <t>+1 604-278-1960</t>
+  </si>
+  <si>
+    <t>5951 Number 3 Rd #570, Richmond, BC V6X 3Y6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lee+Cecilia+Dr/data=!4m7!3m6!1s0x54867533445ee799:0x33cdf3a0d2b3d717!8m2!3d49.1710106!4d-123.1367943!16s%2Fg%2F1tgqj385!19sChIJmedeRDN1hlQRF9ez0qDzzTM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:02.809Z</t>
+  </si>
+  <si>
+    <t>Kao Raymond N K Dr Inc</t>
+  </si>
+  <si>
+    <t>+1 604-207-2255</t>
+  </si>
+  <si>
+    <t>3779 Sexsmith Rd Unit 1292, Richmond, BC V6X 1J8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kao+Raymond+N+K+Dr+Inc/data=!4m7!3m6!1s0x54867526e890eb43:0x56cd61abaf6d227a!8m2!3d49.1856549!4d-123.1302347!16s%2Fg%2F1tdbkpf8!19sChIJQ-uQ6CZ1hlQReiJtr6thzVY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:06.475Z</t>
+  </si>
+  <si>
+    <t>Zhang Dental Clinic / Dr S John Inc</t>
+  </si>
+  <si>
+    <t>+1 604-247-0020</t>
+  </si>
+  <si>
+    <t>8400 Granville Ave Unit 120, Richmond, BC V6Y 4E7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Zhang+Dental+Clinic+%2F+Dr+S+John+Inc/data=!4m7!3m6!1s0x54860ab4ec34726d:0x7b872558671e372d!8m2!3d49.1624447!4d-123.1304795!16s%2Fg%2F1tftqshq!19sChIJbXI07LQKhlQRLTceZ1glh3s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:11.335Z</t>
+  </si>
+  <si>
+    <t>Marine Dental Centre</t>
+  </si>
+  <si>
+    <t>+1 604-278-7778</t>
+  </si>
+  <si>
+    <t>6091 Gilbert Rd. #140, Richmond, BC V7C 5L9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marine+Dental+Centre/data=!4m7!3m6!1s0x54860ace627615a9:0xa9b02cda3e0fcd6!8m2!3d49.1693047!4d-123.1482128!16s%2Fg%2F11b5wjg55l!19sChIJqRV2Ys4KhlQR1vzgo80Cmwo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:40.433Z</t>
+  </si>
+  <si>
+    <t>Dr Janice Sayson</t>
+  </si>
+  <si>
+    <t>+1 604-277-2238</t>
+  </si>
+  <si>
+    <t>9520 Number 3 Rd, Richmond, BC V7A 1W3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Janice+Sayson/data=!4m7!3m6!1s0x54860b37d41e0271:0xf90fbc30e354595d!8m2!3d49.1433856!4d-123.1364173!16s%2Fg%2F11t75mzh8q!19sChIJcQIe1DcLhlQRXVlU4zC8D_k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:42.783Z</t>
+  </si>
+  <si>
+    <t>Cardinal Dental - Dr. Saini</t>
+  </si>
+  <si>
+    <t>+1 604-625-0060</t>
+  </si>
+  <si>
+    <t>30485 Cardinal Ave #210, Abbotsford, BC V2T 0E4, Canada</t>
+  </si>
+  <si>
+    <t>Abbotsford</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cardinal+Dental+-+Dr.+Saini/data=!4m7!3m6!1s0x548435620d7ae41f:0x8712e62e36674e55!8m2!3d49.0611571!4d-122.3794931!16s%2Fg%2F1tfb67l1!19sChIJH-R6DWI1hFQRVU5nNi7mEoc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:56.887Z</t>
+  </si>
+  <si>
+    <t>Abbotsford Dental Group</t>
+  </si>
+  <si>
+    <t>+1 604-853-6441</t>
+  </si>
+  <si>
+    <t>#1, 33782 Marshall Rd #1, Abbotsford, BC V2S 1L1, Canada</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Abbotsford+Dental+Group/data=!4m7!3m6!1s0x54844a982a2d00e1:0x5aa2fd8fbbc212b3!8m2!3d49.0385509!4d-122.2881547!16s%2Fg%2F1tsljdm9!19sChIJ4QAtKphKhFQRsxLCu4_9olo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:59.175Z</t>
+  </si>
+  <si>
+    <t>East West Dental Group</t>
+  </si>
+  <si>
+    <t>+1 604-853-6011</t>
+  </si>
+  <si>
+    <t>32700 South Fraser Way, Abbotsford, BC V2T 4M5, Canada</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/East+West+Dental+Group/data=!4m7!3m6!1s0x5484355b57235929:0x9821a1a56d947753!8m2!3d49.0496565!4d-122.3192219!16s%2Fg%2F1tddxg12!19sChIJKVkjV1s1hFQRU3eUbaWhIZg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:01.033Z</t>
+  </si>
+  <si>
+    <t>Tooth Haven Dental Hygiene</t>
+  </si>
+  <si>
+    <t>+1 778-201-4330</t>
+  </si>
+  <si>
+    <t>Dental hygienist</t>
+  </si>
+  <si>
+    <t>31548 Upper MacLure Rd, Abbotsford, BC V2T 0J3, Canada</t>
+  </si>
+  <si>
+    <t>Sunday10 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tooth+Haven+Dental+Hygiene/data=!4m7!3m6!1s0x5484356313d4eba7:0xce270c301853a379!8m2!3d49.059854!4d-122.3504193!16s%2Fg%2F11vcbd0058!19sChIJp-vUE2M1hFQReaNTGDAMJ84?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:03.087Z</t>
+  </si>
+  <si>
+    <t>Abbotsford Children's Dentistry</t>
+  </si>
+  <si>
+    <t>+1 604-776-3300</t>
+  </si>
+  <si>
+    <t>32625 South Fraser Way #205, Abbotsford, BC V2T 1X8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Abbotsford+Children%27s+Dentistry/data=!4m7!3m6!1s0x54843544bc92d3b7:0xd52537f0de1bfa11!8m2!3d49.0521392!4d-122.32061!16s%2Fg%2F11h193m0lg!19sChIJt9OSvEQ1hFQREfob3vA3JdU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:05.665Z</t>
+  </si>
+  <si>
+    <t>Dr. Andrew Chu, Dentist</t>
+  </si>
+  <si>
+    <t>+1 604-853-5757</t>
+  </si>
+  <si>
+    <t>2216 McCallum Rd #101, Abbotsford, BC V2S 3P3, Canada</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>Open · Closes 5:30 PM · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Andrew+Chu,+Dentist/data=!4m7!3m6!1s0x54844a98c9348aa5:0x696d8c34f5bc4b75!8m2!3d49.0420149!4d-122.2926993!16s%2Fg%2F11b5wqjcxg!19sChIJpYo0yZhKhFQRdUu89TSMbWk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:08.737Z</t>
+  </si>
+  <si>
+    <t>Mill Lake Dental</t>
+  </si>
+  <si>
+    <t>+1 604-852-2171</t>
+  </si>
+  <si>
+    <t>33324 South Fraser Way Unit 10, Abbotsford, BC V2S 2B4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mill+Lake+Dental/data=!4m7!3m6!1s0x5484356121c261c1:0xf1802f40457e0024!8m2!3d49.0496791!4d-122.3009858!16s%2Fg%2F1tdj3x5l!19sChIJwWHCIWE1hFQRJAB-RUAvgPE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:11.086Z</t>
+  </si>
+  <si>
+    <t>Sparkle White Smiles</t>
+  </si>
+  <si>
+    <t>+1 604-556-6534</t>
+  </si>
+  <si>
+    <t>30475 Cardinal Ave #220, Abbotsford, BC V2T 0E5, Canada</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Sunday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sparkle+White+Smiles/data=!4m7!3m6!1s0x548435a3cbb5f373:0x948635ee11e9ec4b!8m2!3d49.060718!4d-122.3794227!16s%2Fg%2F11rsqp4tn_!19sChIJc_O1y6M1hFQRS-zpEe41hpQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:13.110Z</t>
+  </si>
+  <si>
+    <t>Glen Mountain Dental</t>
+  </si>
+  <si>
+    <t>+1 604-852-3151</t>
+  </si>
+  <si>
+    <t>2618 McMillan Rd, Abbotsford, BC V3G 1C4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Glen+Mountain+Dental/data=!4m7!3m6!1s0x54844a7cf2016333:0xedb18033a4a7b70c!8m2!3d49.0497976!4d-122.2598093!16s%2Fg%2F11b5wlfj62!19sChIJM2MB8nxKhFQRDLenpDOAse0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:15.452Z</t>
+  </si>
+  <si>
+    <t>Nurturing Smiles Dental Hygiene Inc</t>
+  </si>
+  <si>
+    <t>+1 778-707-3249</t>
+  </si>
+  <si>
+    <t>2035 Ridgeway St, Abbotsford, BC V2T 3H1, Canada</t>
+  </si>
+  <si>
+    <t>Sunday11 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nurturing+Smiles+Dental+Hygiene+Inc/data=!4m7!3m6!1s0x54844b3155fd0493:0x9ec786093bd835e5!8m2!3d49.0389523!4d-122.3220575!16s%2Fg%2F11ysk9vgv5!19sChIJkwT9VTFLhFQR5TXYOwmGx54?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:18.656Z</t>
+  </si>
+  <si>
+    <t>Tsang Phoebe Dr</t>
+  </si>
+  <si>
+    <t>+1 604-864-0876</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>2051 McCallum Rd #201, Abbotsford, BC V2S 3N3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tsang+Phoebe+Dr/data=!4m7!3m6!1s0x54844aa278bbaf09:0x4ab0781be26450ee!8m2!3d49.0400015!4d-122.2938364!16s%2Fg%2F11v1bp_hj2!19sChIJCa-7eKJKhFQR7lBk4ht4sEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:37.548Z</t>
+  </si>
+  <si>
+    <t>Dr. Michele Wang</t>
+  </si>
+  <si>
+    <t>+1 604-854-5225</t>
+  </si>
+  <si>
+    <t>3033 Immel St, Abbotsford, BC V2S 0E5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michele+Wang/data=!4m7!3m6!1s0x548435444cdc01e9:0xeb5eb26662f92e8f!8m2!3d49.0575982!4d-122.2736648!16s%2Fg%2F1tm68m9n!19sChIJ6QHcTEQ1hFQRjy75YmayXus?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:46.511Z</t>
+  </si>
+  <si>
+    <t>Newtech Dental Laboratory</t>
+  </si>
+  <si>
+    <t>+1 604-853-1199</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>2636 Montrose Ave #201, Abbotsford, BC V2S 3T6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Newtech+Dental+Laboratory/data=!4m7!3m6!1s0x548435629a9a8589:0x6c5f5555a1f70830!8m2!3d49.0499163!4d-122.2900033!16s%2Fg%2F1th56p51!19sChIJiYWammI1hFQRMAj3oVVVX2w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:29:24.668Z</t>
+  </si>
+  <si>
+    <t>Abby Central Medical &amp; Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 604-557-9335</t>
+  </si>
+  <si>
+    <t>2855 Gladwin Rd, Abbotsford, BC V2T 6Y4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Abby+Central+Medical+%26+Dental+Clinic/data=!4m7!3m6!1s0x54843543026a512d:0xe47781fc9e57a02d!8m2!3d49.0540979!4d-122.3176248!16s%2Fg%2F11b6csvfpw!19sChIJLVFqAkM1hFQRLaBXnvyBd-Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:30:03.280Z</t>
+  </si>
+  <si>
+    <t>Venier Ryan Dr</t>
+  </si>
+  <si>
+    <t>+1 604-853-3424</t>
+  </si>
+  <si>
+    <t>34654 Delair Rd Unit 101, Abbotsford, BC V2S 2C9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Venier+Ryan+Dr/data=!4m7!3m6!1s0x54844bc50fec1ec9:0x88cede34e4521da6!8m2!3d49.0344437!4d-122.2629411!16s%2Fg%2F11q57p0tl1!19sChIJyR7sD8VLhFQRph1S5DTezog?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:30:19.466Z</t>
+  </si>
+  <si>
+    <t>HGS Ortho</t>
+  </si>
+  <si>
+    <t>+1 604-464-2527</t>
+  </si>
+  <si>
+    <t>2755 Lougheed Hwy, Port Coquitlam, BC V3B 5Y9, Canada</t>
+  </si>
+  <si>
+    <t>Port Coquitlam</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/HGS+Ortho/data=!4m7!3m6!1s0x54867f4a56e58da9:0xd82b6bdd1a50a87f!8m2!3d49.2741451!4d-122.7885356!16s%2Fg%2F1tncslg_!19sChIJqY3lVkp_hlQRf6hQGt1rK9g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:33:44.696Z</t>
+  </si>
+  <si>
+    <t>Vdo</t>
+  </si>
+  <si>
+    <t>+1 604-944-1573</t>
+  </si>
+  <si>
+    <t>3001 Gordon Ave #204, Coquitlam, BC V3C 2K7, Canada</t>
+  </si>
+  <si>
+    <t>Coquitlam</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vdo/data=!4m7!3m6!1s0x548678b4dff7cac5:0xab0807d3cd983b8f!8m2!3d49.2717863!4d-122.7929287!16s%2Fg%2F1q2wcc4yb!19sChIJxcr337R4hlQRjzuYzdMHCKs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:33:48.384Z</t>
+  </si>
+  <si>
+    <t>Dr. Corlazzoli Cosmetic Dentistry</t>
+  </si>
+  <si>
+    <t>+1 250-861-7088</t>
+  </si>
+  <si>
+    <t>3330 Richter St #110, Kelowna, BC V1W 4V5, Canada</t>
+  </si>
+  <si>
+    <t>Kelowna</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Corlazzoli+Cosmetic+Dentistry/data=!4m7!3m6!1s0x41734ed51aa4ea5f:0xc5f859286aaf2dda!8m2!3d49.8568004!4d-119.4898053!16s%2Fg%2F1q668pc45!19sChIJX-qkGtVOc0ER2i2vaihZ-MU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:37:57.732Z</t>
+  </si>
+  <si>
+    <t>Kelowna Centre for Emergency Dental Care</t>
+  </si>
+  <si>
+    <t>+1 778-484-9522</t>
+  </si>
+  <si>
+    <t>2755 Tutt St, Kelowna, BC V1Y 4Z5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kelowna+Centre+for+Emergency+Dental+Care/data=!4m7!3m6!1s0x537d8b45877ede8f:0x994e54faa2c8e726!8m2!3d49.8655601!4d-119.4900242!16s%2Fg%2F11r4slckbk!19sChIJj95-h0WLfVMRJufIovpUTpk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:39:13.191Z</t>
+  </si>
+  <si>
+    <t>Radiant Renewal Wellness Spa</t>
+  </si>
+  <si>
+    <t>+1 250-718-3767</t>
+  </si>
+  <si>
+    <t>2622 Pandosy St Unit 205, Kelowna, BC V1Y 1V6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Radiant+Renewal+Wellness+Spa/data=!4m7!3m6!1s0x537d8d2000a7f4bd:0xa923c4d25e1d98a2!8m2!3d49.8669645!4d-119.491653!16s%2Fg%2F11h0g6n6zj!19sChIJvfSnACCNfVMRopgdXtLEI6k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:39:50.415Z</t>
+  </si>
+  <si>
+    <t>Stadacona Dental</t>
+  </si>
+  <si>
+    <t>+1 250-595-4144</t>
+  </si>
+  <si>
+    <t>1516 Pandora Ave, Victoria, BC V8R 1A8, Canada</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stadacona+Dental/data=!4m7!3m6!1s0x548f75a7cc411a8d:0x853c88ee8ef84751!8m2!3d48.4268134!4d-123.3376983!16s%2Fg%2F11kqxmydhp!19sChIJjRpBzKd1j1QRUUf4ju6IPIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:44:55.585Z</t>
+  </si>
+  <si>
+    <t>Dr. Garth MacKenzie</t>
+  </si>
+  <si>
+    <t>+1 250-598-8428</t>
+  </si>
+  <si>
+    <t>1830 Oak Bay Ave, Victoria, BC V8R 6R2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Garth+MacKenzie/data=!4m7!3m6!1s0x548f7467dda032d7:0xa5eacc08e1057218!8m2!3d48.4266929!4d-123.3285369!16s%2Fg%2F1tgdsv73!19sChIJ1zKg3Wd0j1QRGHIF4QjM6qU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:44:57.399Z</t>
+  </si>
+  <si>
+    <t>Dr. C. Grady O'Neill</t>
+  </si>
+  <si>
+    <t>+1 250-595-5521</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>3066 Shelbourne St #205, Victoria, BC V8R 6T9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+C.+Grady+O%27Neill/data=!4m7!3m6!1s0x548f747547ad4905:0xa22cfabf6e034681!8m2!3d48.4447145!4d-123.3337802!16s%2Fg%2F1th1cf0j!19sChIJBUmtR3V0j1QRgUYDbr_6LKI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:46:51.756Z</t>
+  </si>
+  <si>
+    <t>Doyle S P Dr</t>
+  </si>
+  <si>
+    <t>+1 250-477-6141</t>
+  </si>
+  <si>
+    <t>3994 Shelbourne St, Victoria, BC V8N 3E2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Doyle+S+P+Dr/data=!4m7!3m6!1s0x548f73df01453e0d:0xfa75f82ba2d072f0!8m2!3d48.4719144!4d-123.3336385!16s%2Fg%2F1ty73zb9!19sChIJDT5FAd9zj1QR8HLQoiv4dfo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:47:27.019Z</t>
+  </si>
+  <si>
+    <t>Prevost Georges Dr</t>
+  </si>
+  <si>
+    <t>+1 250-592-4832</t>
+  </si>
+  <si>
+    <t>3066 Shelbourne St, Victoria, BC V8T 5G1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prevost+Georges+Dr/data=!4m7!3m6!1s0x548f747547ad4905:0xc24841a7fa98dac4!8m2!3d48.4447145!4d-123.3337802!16s%2Fg%2F1tmxf7k9!19sChIJBUmtR3V0j1QRxNqY-qdBSMI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:47:28.860Z</t>
+  </si>
+  <si>
+    <t>West Bay Dental Care</t>
+  </si>
+  <si>
+    <t>+1 250-384-6412</t>
+  </si>
+  <si>
+    <t>474 Head St, Victoria, BC V9A 5S2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Bay+Dental+Care/data=!4m7!3m6!1s0x548f7358dc888e91:0x11a72eecf3464455!8m2!3d48.4265877!4d-123.3992816!16s%2Fg%2F1tf6gb8r!19sChIJkY6I3Fhzj1QRVURG8-wupxE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:47:31.455Z</t>
+  </si>
+  <si>
+    <t>SUPER SMILES TEETH WHITENING CENTRES</t>
+  </si>
+  <si>
+    <t>+1 250-727-6453</t>
+  </si>
+  <si>
+    <t>1644 Hillside Ave #102, Victoria, BC V8T 2C5, Canada</t>
+  </si>
+  <si>
+    <t>Sunday9:30 AM–5:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SUPER+SMILES+TEETH+WHITENING+CENTRES/data=!4m7!3m6!1s0x548f74755e3f7243:0x69f42596ddc285f3!8m2!3d48.4462059!4d-123.3365811!16s%2Fg%2F1v8k_99g!19sChIJQ3I_XnV0j1QR84XC3ZYl9Gk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:48:56.282Z</t>
+  </si>
+  <si>
+    <t>Victoria's Dental Hygiene Clinic</t>
+  </si>
+  <si>
+    <t>+1 250-382-7645</t>
+  </si>
+  <si>
+    <t>1105 Fort St, Victoria, BC V8V 3K8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Victoria%27s+Dental+Hygiene+Clinic/data=!4m7!3m6!1s0x548f7488d21cc2ab:0x1d4aa124664bae68!8m2!3d48.4231603!4d-123.3537432!16s%2Fg%2F1tdrx00v!19sChIJq8Ic0oh0j1QRaK5LZiShSh0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:48:58.907Z</t>
+  </si>
+  <si>
+    <t>Victoria Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 250-999-4377</t>
+  </si>
+  <si>
+    <t>2950 Douglas St Unit 290, Victoria, BC V8T 4N4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Victoria+Dental+Clinic/data=!4m7!3m6!1s0x548f73b9665e649f:0xf274beba990478b7!8m2!3d48.4431379!4d-123.3702045!16s%2Fg%2F11h2gd20tz!19sChIJn2ReZrlzj1QRt3gEmbq-dPI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:49:03.033Z</t>
+  </si>
+  <si>
+    <t>Bild Bernard Dr</t>
+  </si>
+  <si>
+    <t>+1 250-595-6125</t>
+  </si>
+  <si>
+    <t>1750 Richmond Ave, Victoria, BC V8R 4P8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bild+Bernard+Dr/data=!4m7!3m6!1s0x548f7468b088d61f:0xdd23716529d6145d!8m2!3d48.4288978!4d-123.3306198!16s%2Fg%2F1tx4p1gx!19sChIJH9aIsGh0j1QRXRTWKWVxI90?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:49:17.023Z</t>
+  </si>
+  <si>
+    <t>Acadia Dental</t>
+  </si>
+  <si>
+    <t>+1 250-386-8031</t>
+  </si>
+  <si>
+    <t>895 Fort St #216, Victoria, BC V8W 1H6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Acadia+Dental/data=!4m7!3m6!1s0x548f750042cc6179:0xbb93f0c3af2d985c!8m2!3d48.4238847!4d-123.3601139!16s%2Fg%2F11ypz5xndt!19sChIJeWHMQgB1j1QRXJgtr8Pwk7s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:50:55.206Z</t>
+  </si>
+  <si>
+    <t>Chase River Dental</t>
+  </si>
+  <si>
+    <t>+1 250-591-7232</t>
+  </si>
+  <si>
+    <t>51 Tenth St, Nanaimo, BC V9R 6L1, Canada</t>
+  </si>
+  <si>
+    <t>Nanaimo</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chase+River+Dental/data=!4m7!3m6!1s0x5488a43e8fc06c43:0x89b865d34432feea!8m2!3d49.130599!4d-123.9233045!16s%2Fg%2F1tczk537!19sChIJQ2zAjz6kiFQR6v4yRNNluIk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:52:45.813Z</t>
+  </si>
+  <si>
+    <t>Denture Services Nanaimo - Mobile (KDI)</t>
+  </si>
+  <si>
+    <t>+1 604-735-1330</t>
+  </si>
+  <si>
+    <t>1588 Boundary Crescent, Nanaimo, BC V9S 5L5, Canada</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denture+Services+Nanaimo+-+Mobile+%28KDI%29/data=!4m7!3m6!1s0x5488a3ea0d5b947d:0x3da5f51ee472debf!8m2!3d49.1827406!4d-123.9717049!16s%2Fg%2F11ypc6zv05!19sChIJfZRbDeqjiFQRv95y5B71pT0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:52:47.832Z</t>
+  </si>
+  <si>
+    <t>P J Koltronis DDS</t>
+  </si>
+  <si>
+    <t>+1 250-753-4348</t>
+  </si>
+  <si>
+    <t>450 Franklyn St, Nanaimo, BC V9R 2T5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/P+J+Koltronis+DDS/data=!4m7!3m6!1s0x5488a3e2c3580433:0xd82cedda77b3bb7f!8m2!3d49.1638863!4d-123.9403495!16s%2Fg%2F11b5wrb4lx!19sChIJMwRYw-KjiFQRf7uzd9rtLNg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:52:49.988Z</t>
+  </si>
+  <si>
+    <t>Smile Essentials Denture Clinic with Barry Lewis R.D.</t>
+  </si>
+  <si>
+    <t>+1 250-756-1616</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>4515 Uplands Dr, Nanaimo, BC V9T 0M3, Canada</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8:30 AM–4 PM; Tuesday8:30 AM–4 PM; Wednesday8:30 AM–4 PM; Thursday8:30 AM–4 PM; FridayClosed; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smile+Essentials+Denture+Clinic+with+Barry+Lewis+R.D./data=!4m7!3m6!1s0x5488a22f8a571b57:0x68469ab52b2b768d!8m2!3d49.2189733!4d-124.0254428!16s%2Fg%2F1tggt6nc!19sChIJVxtXii-iiFQRjXYrK7WaRmg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:52:54.371Z</t>
+  </si>
+  <si>
+    <t>Pastro Allan Dr Inc</t>
+  </si>
+  <si>
+    <t>+1 250-754-6522</t>
+  </si>
+  <si>
+    <t>140 Wallace St, Nanaimo, BC V9R 5B1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pastro+Allan+Dr+Inc/data=!4m7!3m6!1s0x5488a158abda6ed7:0x3c5d238f98119603!8m2!3d49.1678092!4d-123.9414847!16s%2Fg%2F1ths9141!19sChIJ127aq1ihiFQRA5YRmI8jXTw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:53:09.196Z</t>
+  </si>
+  <si>
+    <t>Paul Shaw-Wood DDS</t>
+  </si>
+  <si>
+    <t>+1 250-248-1041</t>
+  </si>
+  <si>
+    <t>1500 Waddington Rd #1, Nanaimo, BC V9S 4V9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Paul+Shaw-Wood+DDS/data=!4m7!3m6!1s0x5488a17e421342ef:0xe9863c57273fdd86!8m2!3d49.1856899!4d-123.9620494!16s%2Fg%2F11b5wjzgc5!19sChIJ70ITQn6hiFQRht0_J1c8huk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:54:29.910Z</t>
+  </si>
+  <si>
+    <t>True Smiles Smile Spa</t>
+  </si>
+  <si>
+    <t>+1 236-425-0503</t>
+  </si>
+  <si>
+    <t>755 McGill Rd, Kamloops, BC V2C 0B6, Canada</t>
+  </si>
+  <si>
+    <t>Kamloops</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/True+Smiles+Smile+Spa/data=!4m7!3m6!1s0x537e2c5ec23fffff:0x8151d91cbd6ca853!8m2!3d50.6684805!4d-120.3583621!16s%2Fg%2F11gnrlvxv0!19sChIJ__8_wl4sflMRU6hsvRzZUYE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:56:50.308Z</t>
+  </si>
+  <si>
+    <t>Thomson Hugh Dr</t>
+  </si>
+  <si>
+    <t>+1 250-374-5902</t>
+  </si>
+  <si>
+    <t>811 Seymour St, Kamloops, BC V2C 2H6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thomson+Hugh+Dr/data=!4m7!3m6!1s0x537e2daef226f2a1:0xe9b861d6d0558143!8m2!3d50.6748474!4d-120.3210334!16s%2Fg%2F1tgclzsn!19sChIJofIm8q4tflMRQ4FV0NZhuOk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:56:53.760Z</t>
+  </si>
+  <si>
+    <t>Dr. Tracey Murphy</t>
+  </si>
+  <si>
+    <t>+1 250-314-1234</t>
+  </si>
+  <si>
+    <t>629 Lansdowne St #101, Kamloops, BC V2C 1Y6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tracey+Murphy/data=!4m7!3m6!1s0x537e2c5541b4d161:0x19c52f55ebc2d538!8m2!3d50.6765025!4d-120.3262194!16s%2Fg%2F1tg5z9l6!19sChIJYdG0QVUsflMRONXC61UvxRk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:57:01.520Z</t>
+  </si>
+  <si>
+    <t>Dr. Bryce Koronko Inc.</t>
+  </si>
+  <si>
+    <t>+1 250-374-7232</t>
+  </si>
+  <si>
+    <t>MJB Lawyers Professional Building, 275 Lansdowne St, Kamloops, BC V2C 3M2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Bryce+Koronko+Inc./data=!4m7!3m6!1s0x537e2d8def971843:0xf16abaa742c473b6!8m2!3d50.6764594!4d-120.3348496!16s%2Fg%2F11fjy3w2vw!19sChIJQxiX740tflMRtnPEQqe6avE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:57:03.531Z</t>
+  </si>
+  <si>
+    <t>McLean Alex Dr</t>
+  </si>
+  <si>
+    <t>+1 250-851-7668</t>
+  </si>
+  <si>
+    <t>301 Victoria St, Kamloops, BC V2C 2A3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/McLean+Alex+Dr/data=!4m7!3m6!1s0x537e2dab2e8da03b:0x1eaebf7dfb3849c!8m2!3d50.6756028!4d-120.3340511!16s%2Fg%2F1tfc68vc!19sChIJO6CNLqstflMRnISz3_fr6gE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:57:26.589Z</t>
+  </si>
+  <si>
+    <t>Kamloops Centre-Laser Dentistry</t>
+  </si>
+  <si>
+    <t>+1 250-579-8105</t>
+  </si>
+  <si>
+    <t>3122 Westsyde Rd, Kamloops, BC V2B 7G4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kamloops+Centre-Laser+Dentistry/data=!4m7!3m6!1s0x537fcd793cb346cf:0xfaf954ea536b81b8!8m2!3d50.7634168!4d-120.3483737!16s%2Fg%2F1tgdstmj!19sChIJz0azPHnNf1MRuIFrU-pU-fo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:57:50.281Z</t>
+  </si>
+  <si>
+    <t>Dr. Jason Heilmann</t>
+  </si>
+  <si>
+    <t>+1 250-372-1237</t>
+  </si>
+  <si>
+    <t>444 Victoria St, Kamloops, BC V2C 2A7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jason+Heilmann/data=!4m7!3m6!1s0x537e2dab2f223d39:0xe6424f877ac1e41c!8m2!3d50.6760891!4d-120.3305712!16s%2Fg%2F11btz33rgn!19sChIJOT0iL6stflMRHOTBeodPQuY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:58:22.742Z</t>
+  </si>
+  <si>
+    <t>Cottonwood Mall Dental Ctr</t>
+  </si>
+  <si>
+    <t>+1 604-858-8171</t>
+  </si>
+  <si>
+    <t>45585 Luckakuck Way #35, Chilliwack, BC V2R 1A1, Canada</t>
+  </si>
+  <si>
+    <t>Chilliwack</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cottonwood+Mall+Dental+Ctr/data=!4m7!3m6!1s0x548440a4bb7f5615:0x8871ed9596acd2e6!8m2!3d49.1422336!4d-121.9636491!16s%2Fg%2F1tgb_g4x!19sChIJFVZ_u6RAhFQR5tKslpXtcYg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:59:52.515Z</t>
+  </si>
+  <si>
+    <t>Aura Denture Clinic - Chilliwack</t>
+  </si>
+  <si>
+    <t>+1 604-853-7793</t>
+  </si>
+  <si>
+    <t>45485 Knight Rd #205, Chilliwack, BC V2R 3G3, Canada</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aura+Denture+Clinic+-+Chilliwack/data=!4m7!3m6!1s0x5484417c1b1b71d3:0x998d110e9e26f342!8m2!3d49.1399713!4d-121.966129!16s%2Fg%2F11zfpdmnxp!19sChIJ03EbG3xBhFQRQvMmng4RjZk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:00:40.664Z</t>
+  </si>
+  <si>
+    <t>Jadvinder Dhesi Inc</t>
+  </si>
+  <si>
+    <t>+1 604-792-3324</t>
+  </si>
+  <si>
+    <t>9123 Mary St, Chilliwack, BC V2P 4H7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jadvinder+Dhesi+Inc/data=!4m7!3m6!1s0x54843f719cad0313:0x487d959fcc2a8afc!8m2!3d49.1679785!4d-121.961218!16s%2Fg%2F1tknk3ms!19sChIJEwOtnHE_hFQR_IoqzJ-VfUg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:00:42.678Z</t>
+  </si>
+  <si>
+    <t>Sims Barbara Dr</t>
+  </si>
+  <si>
+    <t>+1 604-858-5921</t>
+  </si>
+  <si>
+    <t>45485 Knight Rd, Chilliwack, BC V2R 3G3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sims+Barbara+Dr/data=!4m7!3m6!1s0x548440a53edcb63d:0x1310af3136e04471!8m2!3d49.139804!4d-121.965522!16s%2Fg%2F1vfp39r_!19sChIJPbbcPqVAhFQRcUTgNjGvEBM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:00:45.023Z</t>
+  </si>
+  <si>
+    <t>Canadian Aligner Club Chilliwack Salish Plaza</t>
+  </si>
+  <si>
+    <t>+1 604-792-6999</t>
+  </si>
+  <si>
+    <t>46030 Yale Rd Unit 25, Chilliwack, BC V2P 7V2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Canadian+Aligner+Club+Chilliwack+Salish+Plaza/data=!4m7!3m6!1s0x54843f6ca9bf0b67:0x47d09906d3946f7d!8m2!3d49.1690691!4d-121.9534103!16s%2Fg%2F11r_vc8rrq!19sChIJZwu_qWw_hFQRfW-U0waZ0Ec?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:00:48.454Z</t>
+  </si>
+  <si>
+    <t>Huang Mark Dr</t>
+  </si>
+  <si>
+    <t>+1 604-792-6616</t>
+  </si>
+  <si>
+    <t>45780 Yale Rd #2, Chilliwack, BC V2P 2N4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Huang+Mark+Dr/data=!4m7!3m6!1s0x54843f65374248f9:0x8a2cc2193c6dfc6f!8m2!3d49.1621971!4d-121.9582825!16s%2Fg%2F1v8k_8xf!19sChIJ-UhCN2U_hFQRb_xtPBnCLIo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:00:50.562Z</t>
+  </si>
+  <si>
+    <t>Chilliwack Pediatric Clinic</t>
+  </si>
+  <si>
+    <t>+1 604-793-4508</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>ave 1p3, 45543 Hodgins Ave, Chilliwack, BC V2P 1P3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chilliwack+Pediatric+Clinic/data=!4m7!3m6!1s0x54843f6df76987a9:0x6476182dea1556c5!8m2!3d49.167428!4d-121.9652663!16s%2Fg%2F11b6_k9mw4!19sChIJqYdp920_hFQRxVYV6i0YdmQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:01:33.501Z</t>
+  </si>
+  <si>
+    <t>Haghi &amp; Sefidpour Drs Inc</t>
+  </si>
+  <si>
+    <t>+1 604-792-5722</t>
+  </si>
+  <si>
+    <t>45610 Yale Rd, Chilliwack, BC V2P 2N3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Haghi+%26+Sefidpour+Drs+Inc/data=!4m7!3m6!1s0x54843f610ee688f3:0xaa02b4b82315f9c0!8m2!3d49.153739!4d-121.961946!16s%2Fg%2F1pyqfh_gb!19sChIJ84jmDmE_hFQRwPkVI7i0Aqo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:01:42.558Z</t>
+  </si>
+  <si>
+    <t>Cheam View Veterinary Hospital</t>
+  </si>
+  <si>
+    <t>+1 604-795-5721</t>
+  </si>
+  <si>
+    <t>Veterinarian</t>
+  </si>
+  <si>
+    <t>8337 Young Rd, Chilliwack, BC V2P 4N8, Canada</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Open · Closes 10 PM · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cheam+View+Veterinary+Hospital/data=!4m7!3m6!1s0x5484409d70f9344d:0xc67dcd5379b5ed92!8m2!3d49.1536061!4d-121.951986!16s%2Fg%2F1vd3vgzq!19sChIJTTT5cJ1AhFQRku21eVPNfcY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:02:17.976Z</t>
+  </si>
+  <si>
+    <t>Mira Percovic DDS</t>
+  </si>
+  <si>
+    <t>+1 250-960-3813</t>
+  </si>
+  <si>
+    <t>760 Kinsmen Pl, Prince George, BC V2M 0A8, Canada</t>
+  </si>
+  <si>
+    <t>Prince George</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mira+Percovic+DDS/data=!4m7!3m6!1s0x53889974aa5809f7:0x1a6cb27a179e1c47!8m2!3d53.9202519!4d-122.7916262!16s%2Fg%2F1ptx163xm!19sChIJ9wlYqnSZiFMRRxyeF3qybBo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:03:25.756Z</t>
+  </si>
+  <si>
+    <t>Pastro Kris Dr</t>
+  </si>
+  <si>
+    <t>+1 250-960-3809</t>
+  </si>
+  <si>
+    <t>4122 15th Ave, Prince George, BC V2M 1V9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pastro+Kris+Dr/data=!4m7!3m6!1s0x53889974aa5809f7:0xea961d1e5674fd4c!8m2!3d53.9107335!4d-122.7992375!16s%2Fg%2F1tdy_n3h!19sChIJ9wlYqnSZiFMRTP10Vh4dluo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:03:42.297Z</t>
+  </si>
+  <si>
+    <t>Austin Dental Building</t>
+  </si>
+  <si>
+    <t>+1 250-962-5351</t>
+  </si>
+  <si>
+    <t>3652 Austin Rd W #3644, Prince George, BC V2K 2H6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Austin+Dental+Building/data=!4m7!3m6!1s0x538897bd1474ac19:0xc4c4751102cb9192!8m2!3d53.9896102!4d-122.7879864!16s%2Fg%2F11g03wrkv6!19sChIJGax0FL2XiFMRkpHLAhF1xMQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:03:51.729Z</t>
+  </si>
+  <si>
+    <t>Corbett I Keith Dr</t>
+  </si>
+  <si>
+    <t>+1 250-563-7223</t>
+  </si>
+  <si>
+    <t>1576 7 Ave, Prince George, BC V2L 3P4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Corbett+I+Keith+Dr/data=!4m7!3m6!1s0x538898e3a797c6c5:0xd04ccbc957c9213c!8m2!3d53.9152809!4d-122.7526369!16s%2Fg%2F1hc5g9gpw!19sChIJxcaXp-OYiFMRPCHJV8nLTNA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:03:55.172Z</t>
+  </si>
+  <si>
+    <t>Prince George Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>+1 250-596-2202</t>
+  </si>
+  <si>
+    <t>1669 Victoria St #209, Prince George, BC V2L 2L5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prince+George+Pediatric+Dentistry/data=!4m7!3m6!1s0x53889943e9bf9297:0x5909167d875b6d91!8m2!3d53.9088196!4d-122.7554224!16s%2Fg%2F11mcj_s565!19sChIJl5K_6UOZiFMRkW1bh30WCVk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:00.176Z</t>
+  </si>
+  <si>
+    <t>Kjorven Diane Dr Inc</t>
+  </si>
+  <si>
+    <t>+1 250-564-7337</t>
+  </si>
+  <si>
+    <t>1531 8 Ave, Prince George, BC V2L 3R3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kjorven+Diane+Dr+Inc/data=!4m7!3m6!1s0x538898e3b3451705:0xadb4570c3976d5cb!8m2!3d53.914088!4d-122.7529481!16s%2Fg%2F1tdmv945!19sChIJBRdFs-OYiFMRy9V2OQxXtK0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:03.547Z</t>
+  </si>
+  <si>
+    <t>Wellhouse Dental</t>
+  </si>
+  <si>
+    <t>+1 250-563-9397</t>
+  </si>
+  <si>
+    <t>1580 10th Ave, Prince George, BC V2M 1V9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wellhouse+Dental/data=!4m7!3m6!1s0x538898e2154d93b3:0xe234f829492a11a0!8m2!3d53.9130864!4d-122.754502!16s%2Fg%2F11fnwgw9x4!19sChIJs5NNFeKYiFMRoBEqSSn4NOI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:18.633Z</t>
+  </si>
+  <si>
+    <t>North Central Dental Arts Inc</t>
+  </si>
+  <si>
+    <t>+1 250-562-4227</t>
+  </si>
+  <si>
+    <t>498 Ospika Blvd S, Prince George, BC V2M 3R3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Central+Dental+Arts+Inc/data=!4m7!3m6!1s0x538899a7a6773ee1:0xb909986d3651812c!8m2!3d53.9202834!4d-122.7918861!16s%2Fg%2F1tczdl6y!19sChIJ4T53pqeZiFMRLIFRNm2YCbk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:20.733Z</t>
+  </si>
+  <si>
+    <t>Foothills Plaza Dental Clinic</t>
+  </si>
+  <si>
+    <t>+1 250-960-3818</t>
+  </si>
+  <si>
+    <t>4174 15th Ave, Prince George, BC V2M 1V8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Foothills+Plaza+Dental+Clinic/data=!4m7!3m6!1s0x53889974967fb2f5:0x844a2dbca7ef7d33!8m2!3d53.910648!4d-122.8010607!16s%2Fg%2F11b5wpdlfb!19sChIJ9bJ_lnSZiFMRM33vp7wtSoQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:25.860Z</t>
+  </si>
+  <si>
+    <t>Mann Satish Dr Inc</t>
+  </si>
+  <si>
+    <t>+1 250-564-6211</t>
+  </si>
+  <si>
+    <t>2155 10th Ave #308, Prince George, BC V2M 5J6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mann+Satish+Dr+Inc/data=!4m7!3m6!1s0x5388990320f129db:0x463f1c971810ed1f!8m2!3d53.9148995!4d-122.7657784!16s%2Fg%2F1tjs4m8h!19sChIJ2ynxIAOZiFMRH-0QGJccP0Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:28.379Z</t>
+  </si>
+  <si>
+    <t>Hamour a a Dr</t>
+  </si>
+  <si>
+    <t>+1 250-563-8284</t>
+  </si>
+  <si>
+    <t>925 Vancouver St, Prince George, BC V2L 2P6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hamour+a+a+Dr/data=!4m7!3m6!1s0x53889902d899d0b3:0xeb70684fc92d7aa4!8m2!3d53.9136448!4d-122.755064!16s%2Fg%2F11cn_9q1kp!19sChIJs9CZ2AKZiFMRpHotyU9ocOs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:30.734Z</t>
+  </si>
+  <si>
+    <t>Queen Bee Beauty</t>
+  </si>
+  <si>
+    <t>+1 250-613-1946</t>
+  </si>
+  <si>
+    <t>Beauty salon</t>
+  </si>
+  <si>
+    <t>3980 Cummings Rd, Prince George, BC V2N 6E8, Canada</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Queen+Bee+Beauty/data=!4m7!3m6!1s0x16a39a9734459df:0x176cc6cc1f2b78fd!8m2!3d53.8518104!4d-122.6709684!16s%2Fg%2F11q45fwhls!19sChIJ31lEc6k5agER_XgrH8zGbBc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:04:52.460Z</t>
+  </si>
+  <si>
+    <t>Heritage Orthopaedic Group</t>
+  </si>
+  <si>
+    <t>+1 250-564-8800</t>
+  </si>
+  <si>
+    <t>1624 7 Ave, Prince George, BC V2L 3P6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Heritage+Orthopaedic+Group/data=!4m7!3m6!1s0x538898e305d08947:0x37dc1ff4fb60cf97!8m2!3d53.9156896!4d-122.7536897!16s%2Fg%2F1tgjkzf2!19sChIJR4nQBeOYiFMRl89g-_Qf3Dc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T23:05:06.612Z</t>
   </si>
 </sst>
 </file>
@@ -844,7 +2152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1763,6 +3071,3286 @@
         <v>150</v>
       </c>
     </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>147</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>164</v>
+      </c>
+      <c r="M25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>169</v>
+      </c>
+      <c r="M26" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>174</v>
+      </c>
+      <c r="M27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>179</v>
+      </c>
+      <c r="M28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>184</v>
+      </c>
+      <c r="M29" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>189</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>190</v>
+      </c>
+      <c r="M30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>195</v>
+      </c>
+      <c r="M31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>42</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>200</v>
+      </c>
+      <c r="M32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>42</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>205</v>
+      </c>
+      <c r="M33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>100</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>210</v>
+      </c>
+      <c r="M34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>215</v>
+      </c>
+      <c r="M35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>220</v>
+      </c>
+      <c r="M36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" t="s">
+        <v>225</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>100</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>226</v>
+      </c>
+      <c r="M37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>228</v>
+      </c>
+      <c r="B38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>147</v>
+      </c>
+      <c r="I38" t="s">
+        <v>231</v>
+      </c>
+      <c r="J38" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>232</v>
+      </c>
+      <c r="M38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>236</v>
+      </c>
+      <c r="E39" t="s">
+        <v>225</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>237</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>238</v>
+      </c>
+      <c r="M39" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>244</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>245</v>
+      </c>
+      <c r="M40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" t="s">
+        <v>225</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>250</v>
+      </c>
+      <c r="M41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" t="s">
+        <v>225</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>255</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>256</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M42" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>259</v>
+      </c>
+      <c r="B43" t="s">
+        <v>260</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" t="s">
+        <v>225</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>189</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>262</v>
+      </c>
+      <c r="M43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>267</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>268</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>269</v>
+      </c>
+      <c r="M44" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>271</v>
+      </c>
+      <c r="B45" t="s">
+        <v>272</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>273</v>
+      </c>
+      <c r="E45" t="s">
+        <v>225</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>274</v>
+      </c>
+      <c r="M45" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>276</v>
+      </c>
+      <c r="B46" t="s">
+        <v>277</v>
+      </c>
+      <c r="C46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" t="s">
+        <v>278</v>
+      </c>
+      <c r="E46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>279</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>280</v>
+      </c>
+      <c r="M46" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>282</v>
+      </c>
+      <c r="B47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C47" t="s">
+        <v>284</v>
+      </c>
+      <c r="D47" t="s">
+        <v>285</v>
+      </c>
+      <c r="E47" t="s">
+        <v>225</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" t="s">
+        <v>43</v>
+      </c>
+      <c r="J47" t="s">
+        <v>42</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>286</v>
+      </c>
+      <c r="M47" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>288</v>
+      </c>
+      <c r="B48" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s">
+        <v>290</v>
+      </c>
+      <c r="E48" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>291</v>
+      </c>
+      <c r="M48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>293</v>
+      </c>
+      <c r="B49" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>297</v>
+      </c>
+      <c r="M49" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" t="s">
+        <v>300</v>
+      </c>
+      <c r="C50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" t="s">
+        <v>301</v>
+      </c>
+      <c r="E50" t="s">
+        <v>225</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>267</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>302</v>
+      </c>
+      <c r="M50" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" t="s">
+        <v>305</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>306</v>
+      </c>
+      <c r="E51" t="s">
+        <v>225</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" t="s">
+        <v>43</v>
+      </c>
+      <c r="J51" t="s">
+        <v>42</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>307</v>
+      </c>
+      <c r="M51" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>309</v>
+      </c>
+      <c r="B52" t="s">
+        <v>310</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" t="s">
+        <v>311</v>
+      </c>
+      <c r="E52" t="s">
+        <v>312</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>313</v>
+      </c>
+      <c r="M52" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>315</v>
+      </c>
+      <c r="B53" t="s">
+        <v>316</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>317</v>
+      </c>
+      <c r="E53" t="s">
+        <v>318</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>319</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>320</v>
+      </c>
+      <c r="M53" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>324</v>
+      </c>
+      <c r="E54" t="s">
+        <v>325</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>326</v>
+      </c>
+      <c r="M54" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>328</v>
+      </c>
+      <c r="B55" t="s">
+        <v>329</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>330</v>
+      </c>
+      <c r="E55" t="s">
+        <v>325</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" t="s">
+        <v>42</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>331</v>
+      </c>
+      <c r="M55" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>333</v>
+      </c>
+      <c r="B56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C56" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" t="s">
+        <v>335</v>
+      </c>
+      <c r="E56" t="s">
+        <v>325</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>42</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>336</v>
+      </c>
+      <c r="M56" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>338</v>
+      </c>
+      <c r="B57" t="s">
+        <v>339</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>340</v>
+      </c>
+      <c r="E57" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>342</v>
+      </c>
+      <c r="M57" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>346</v>
+      </c>
+      <c r="E58" t="s">
+        <v>341</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>50</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>42</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>347</v>
+      </c>
+      <c r="M58" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>349</v>
+      </c>
+      <c r="B59" t="s">
+        <v>350</v>
+      </c>
+      <c r="C59" t="s">
+        <v>351</v>
+      </c>
+      <c r="D59" t="s">
+        <v>352</v>
+      </c>
+      <c r="E59" t="s">
+        <v>341</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>107</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>353</v>
+      </c>
+      <c r="M59" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>355</v>
+      </c>
+      <c r="B60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>357</v>
+      </c>
+      <c r="E60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>42</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>358</v>
+      </c>
+      <c r="M60" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>360</v>
+      </c>
+      <c r="B61" t="s">
+        <v>361</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>362</v>
+      </c>
+      <c r="E61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>100</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>363</v>
+      </c>
+      <c r="M61" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>365</v>
+      </c>
+      <c r="B62" t="s">
+        <v>366</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>367</v>
+      </c>
+      <c r="E62" t="s">
+        <v>341</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>76</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>42</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>368</v>
+      </c>
+      <c r="M62" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>370</v>
+      </c>
+      <c r="B63" t="s">
+        <v>371</v>
+      </c>
+      <c r="C63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" t="s">
+        <v>372</v>
+      </c>
+      <c r="E63" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>373</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>374</v>
+      </c>
+      <c r="M63" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>376</v>
+      </c>
+      <c r="B64" t="s">
+        <v>377</v>
+      </c>
+      <c r="C64" t="s">
+        <v>144</v>
+      </c>
+      <c r="D64" t="s">
+        <v>378</v>
+      </c>
+      <c r="E64" t="s">
+        <v>341</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>29</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>379</v>
+      </c>
+      <c r="M64" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>381</v>
+      </c>
+      <c r="B65" t="s">
+        <v>382</v>
+      </c>
+      <c r="C65" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" t="s">
+        <v>383</v>
+      </c>
+      <c r="E65" t="s">
+        <v>341</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>384</v>
+      </c>
+      <c r="M65" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>386</v>
+      </c>
+      <c r="B66" t="s">
+        <v>387</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>388</v>
+      </c>
+      <c r="E66" t="s">
+        <v>341</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>42</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>389</v>
+      </c>
+      <c r="M66" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>391</v>
+      </c>
+      <c r="B67" t="s">
+        <v>392</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>393</v>
+      </c>
+      <c r="E67" t="s">
+        <v>341</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>42</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>394</v>
+      </c>
+      <c r="M67" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>396</v>
+      </c>
+      <c r="B68" t="s">
+        <v>397</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>398</v>
+      </c>
+      <c r="E68" t="s">
+        <v>399</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>400</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>401</v>
+      </c>
+      <c r="M68" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>403</v>
+      </c>
+      <c r="B69" t="s">
+        <v>404</v>
+      </c>
+      <c r="C69" t="s">
+        <v>144</v>
+      </c>
+      <c r="D69" t="s">
+        <v>405</v>
+      </c>
+      <c r="E69" t="s">
+        <v>399</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>42</v>
+      </c>
+      <c r="I69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" t="s">
+        <v>406</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>407</v>
+      </c>
+      <c r="M69" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>409</v>
+      </c>
+      <c r="B70" t="s">
+        <v>410</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>411</v>
+      </c>
+      <c r="E70" t="s">
+        <v>399</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>412</v>
+      </c>
+      <c r="M70" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" t="s">
+        <v>415</v>
+      </c>
+      <c r="C71" t="s">
+        <v>416</v>
+      </c>
+      <c r="D71" t="s">
+        <v>417</v>
+      </c>
+      <c r="E71" t="s">
+        <v>399</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>267</v>
+      </c>
+      <c r="I71" t="s">
+        <v>418</v>
+      </c>
+      <c r="J71" t="s">
+        <v>419</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>420</v>
+      </c>
+      <c r="M71" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>422</v>
+      </c>
+      <c r="B72" t="s">
+        <v>423</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>424</v>
+      </c>
+      <c r="E72" t="s">
+        <v>399</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>29</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>42</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>425</v>
+      </c>
+      <c r="M72" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>427</v>
+      </c>
+      <c r="B73" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>429</v>
+      </c>
+      <c r="E73" t="s">
+        <v>399</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>56</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>42</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>432</v>
+      </c>
+      <c r="B74" t="s">
+        <v>433</v>
+      </c>
+      <c r="C74" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" t="s">
+        <v>434</v>
+      </c>
+      <c r="E74" t="s">
+        <v>435</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>29</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>436</v>
+      </c>
+      <c r="M74" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>438</v>
+      </c>
+      <c r="B75" t="s">
+        <v>439</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>440</v>
+      </c>
+      <c r="E75" t="s">
+        <v>435</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>100</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>441</v>
+      </c>
+      <c r="M75" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>443</v>
+      </c>
+      <c r="B76" t="s">
+        <v>444</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>445</v>
+      </c>
+      <c r="E76" t="s">
+        <v>435</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" t="s">
+        <v>43</v>
+      </c>
+      <c r="J76" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>446</v>
+      </c>
+      <c r="M76" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>448</v>
+      </c>
+      <c r="B77" t="s">
+        <v>449</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>450</v>
+      </c>
+      <c r="E77" t="s">
+        <v>435</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>22</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>451</v>
+      </c>
+      <c r="M77" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>453</v>
+      </c>
+      <c r="B78" t="s">
+        <v>454</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>455</v>
+      </c>
+      <c r="E78" t="s">
+        <v>435</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>147</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>456</v>
+      </c>
+      <c r="M78" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>458</v>
+      </c>
+      <c r="B79" t="s">
+        <v>459</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" t="s">
+        <v>460</v>
+      </c>
+      <c r="E79" t="s">
+        <v>435</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>29</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>42</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>461</v>
+      </c>
+      <c r="M79" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>463</v>
+      </c>
+      <c r="B80" t="s">
+        <v>464</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>465</v>
+      </c>
+      <c r="E80" t="s">
+        <v>435</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>319</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>466</v>
+      </c>
+      <c r="M80" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>468</v>
+      </c>
+      <c r="B81" t="s">
+        <v>469</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>470</v>
+      </c>
+      <c r="E81" t="s">
+        <v>471</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>147</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>472</v>
+      </c>
+      <c r="M81" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>474</v>
+      </c>
+      <c r="B82" t="s">
+        <v>475</v>
+      </c>
+      <c r="C82" t="s">
+        <v>416</v>
+      </c>
+      <c r="D82" t="s">
+        <v>476</v>
+      </c>
+      <c r="E82" t="s">
+        <v>471</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" t="s">
+        <v>477</v>
+      </c>
+      <c r="J82" t="s">
+        <v>42</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>478</v>
+      </c>
+      <c r="M82" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>480</v>
+      </c>
+      <c r="B83" t="s">
+        <v>481</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" t="s">
+        <v>482</v>
+      </c>
+      <c r="E83" t="s">
+        <v>471</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>107</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>42</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>483</v>
+      </c>
+      <c r="M83" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>485</v>
+      </c>
+      <c r="B84" t="s">
+        <v>486</v>
+      </c>
+      <c r="C84" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" t="s">
+        <v>487</v>
+      </c>
+      <c r="E84" t="s">
+        <v>471</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>42</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>488</v>
+      </c>
+      <c r="M84" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>490</v>
+      </c>
+      <c r="B85" t="s">
+        <v>491</v>
+      </c>
+      <c r="C85" t="s">
+        <v>117</v>
+      </c>
+      <c r="D85" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" t="s">
+        <v>471</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" t="s">
+        <v>22</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>493</v>
+      </c>
+      <c r="M85" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>495</v>
+      </c>
+      <c r="B86" t="s">
+        <v>496</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>497</v>
+      </c>
+      <c r="E86" t="s">
+        <v>471</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>70</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>22</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>498</v>
+      </c>
+      <c r="M86" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>500</v>
+      </c>
+      <c r="B87" t="s">
+        <v>501</v>
+      </c>
+      <c r="C87" t="s">
+        <v>502</v>
+      </c>
+      <c r="D87" t="s">
+        <v>503</v>
+      </c>
+      <c r="E87" t="s">
+        <v>471</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>29</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>504</v>
+      </c>
+      <c r="M87" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>506</v>
+      </c>
+      <c r="B88" t="s">
+        <v>507</v>
+      </c>
+      <c r="C88" t="s">
+        <v>117</v>
+      </c>
+      <c r="D88" t="s">
+        <v>508</v>
+      </c>
+      <c r="E88" t="s">
+        <v>471</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" t="s">
+        <v>43</v>
+      </c>
+      <c r="J88" t="s">
+        <v>42</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>509</v>
+      </c>
+      <c r="M88" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>511</v>
+      </c>
+      <c r="B89" t="s">
+        <v>512</v>
+      </c>
+      <c r="C89" t="s">
+        <v>513</v>
+      </c>
+      <c r="D89" t="s">
+        <v>514</v>
+      </c>
+      <c r="E89" t="s">
+        <v>471</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>515</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>516</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>517</v>
+      </c>
+      <c r="M89" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>519</v>
+      </c>
+      <c r="B90" t="s">
+        <v>520</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>521</v>
+      </c>
+      <c r="E90" t="s">
+        <v>522</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>29</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>406</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>523</v>
+      </c>
+      <c r="M90" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>525</v>
+      </c>
+      <c r="B91" t="s">
+        <v>526</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>527</v>
+      </c>
+      <c r="E91" t="s">
+        <v>522</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>29</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>42</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>528</v>
+      </c>
+      <c r="M91" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>530</v>
+      </c>
+      <c r="B92" t="s">
+        <v>531</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>532</v>
+      </c>
+      <c r="E92" t="s">
+        <v>522</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>533</v>
+      </c>
+      <c r="M92" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>535</v>
+      </c>
+      <c r="B93" t="s">
+        <v>536</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>537</v>
+      </c>
+      <c r="E93" t="s">
+        <v>522</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>538</v>
+      </c>
+      <c r="M93" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>540</v>
+      </c>
+      <c r="B94" t="s">
+        <v>541</v>
+      </c>
+      <c r="C94" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" t="s">
+        <v>542</v>
+      </c>
+      <c r="E94" t="s">
+        <v>522</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>543</v>
+      </c>
+      <c r="M94" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>545</v>
+      </c>
+      <c r="B95" t="s">
+        <v>546</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>547</v>
+      </c>
+      <c r="E95" t="s">
+        <v>522</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>147</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>42</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>548</v>
+      </c>
+      <c r="M95" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>550</v>
+      </c>
+      <c r="B96" t="s">
+        <v>551</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>552</v>
+      </c>
+      <c r="E96" t="s">
+        <v>522</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>255</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>553</v>
+      </c>
+      <c r="M96" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>555</v>
+      </c>
+      <c r="B97" t="s">
+        <v>556</v>
+      </c>
+      <c r="C97" t="s">
+        <v>295</v>
+      </c>
+      <c r="D97" t="s">
+        <v>557</v>
+      </c>
+      <c r="E97" t="s">
+        <v>522</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" t="s">
+        <v>42</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>558</v>
+      </c>
+      <c r="M97" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>560</v>
+      </c>
+      <c r="B98" t="s">
+        <v>561</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>562</v>
+      </c>
+      <c r="E98" t="s">
+        <v>522</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>42</v>
+      </c>
+      <c r="I98" t="s">
+        <v>43</v>
+      </c>
+      <c r="J98" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>563</v>
+      </c>
+      <c r="M98" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>565</v>
+      </c>
+      <c r="B99" t="s">
+        <v>566</v>
+      </c>
+      <c r="C99" t="s">
+        <v>502</v>
+      </c>
+      <c r="D99" t="s">
+        <v>567</v>
+      </c>
+      <c r="E99" t="s">
+        <v>522</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>29</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>568</v>
+      </c>
+      <c r="M99" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>570</v>
+      </c>
+      <c r="B100" t="s">
+        <v>571</v>
+      </c>
+      <c r="C100" t="s">
+        <v>502</v>
+      </c>
+      <c r="D100" t="s">
+        <v>572</v>
+      </c>
+      <c r="E100" t="s">
+        <v>522</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>255</v>
+      </c>
+      <c r="I100" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s">
+        <v>42</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>573</v>
+      </c>
+      <c r="M100" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>575</v>
+      </c>
+      <c r="B101" t="s">
+        <v>576</v>
+      </c>
+      <c r="C101" t="s">
+        <v>577</v>
+      </c>
+      <c r="D101" t="s">
+        <v>578</v>
+      </c>
+      <c r="E101" t="s">
+        <v>522</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>29</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>579</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>580</v>
+      </c>
+      <c r="M101" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>582</v>
+      </c>
+      <c r="B102" t="s">
+        <v>583</v>
+      </c>
+      <c r="C102" t="s">
+        <v>502</v>
+      </c>
+      <c r="D102" t="s">
+        <v>584</v>
+      </c>
+      <c r="E102" t="s">
+        <v>522</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>76</v>
+      </c>
+      <c r="I102" t="s">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>585</v>
+      </c>
+      <c r="M102" t="s">
+        <v>586</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
